--- a/data.xlsx
+++ b/data.xlsx
@@ -25,10 +25,10 @@
     <t xml:space="preserve">編號</t>
   </si>
   <si>
-    <t xml:space="preserve">姓名</t>
+    <t xml:space="preserve">名稱</t>
   </si>
   <si>
-    <t xml:space="preserve">座位</t>
+    <t xml:space="preserve">位置</t>
   </si>
   <si>
     <t xml:space="preserve">備註</t>

--- a/data.xlsx
+++ b/data.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t xml:space="preserve">編號</t>
   </si>
@@ -47,6 +47,9 @@
   </si>
   <si>
     <t xml:space="preserve">BRACKET</t>
+  </si>
+  <si>
+    <t xml:space="preserve">x</t>
   </si>
 </sst>
 </file>
@@ -244,6 +247,9 @@
       <c r="B3" s="5" t="s">
         <v>8</v>
       </c>
+      <c r="C3" s="0" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -215,7 +215,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="3" style="0" width="12.07"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
